--- a/output/full_scan/batch_seq8_2026-06-30.xlsx
+++ b/output/full_scan/batch_seq8_2026-06-30.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>968.169200475194</v>
+        <v>1138.169200475194</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>332</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>64.22349430665832</v>
+        <v>64.22349431706297</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>38.11151429017325</v>
+        <v>38.11151424260031</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.704249850265246</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.620436066571331</v>
+        <v>1.620436066285134</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>787.5540919361671</v>
+        <v>1057.554091936167</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>317</v>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>55.6019145616425</v>
+        <v>55.60191458251241</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>32.84335437077905</v>
+        <v>32.84335435027048</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.638540748291477</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-4.67831926063162</v>
+        <v>-4.678319261490213</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7795</v>
+        <v>6928</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>746.2262432943159</v>
+        <v>1006.195522226755</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>556</v>
+        <v>54.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>74.67740147161186</v>
+        <v>70.54676223387899</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>20.74456233244841</v>
+        <v>26.20103875019534</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.722624329431582</v>
+        <v>4.219552222675538</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>15.28850835633096</v>
+        <v>0.7461601312755932</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8040</v>
+        <v>8033</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>742.6540513625089</v>
+        <v>994</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>112</v>
+        <v>169.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>57.23298052459945</v>
+        <v>74.86076911561834</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>34.20765434785674</v>
+        <v>16.93536303772281</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.7718645959272675</v>
+        <v>6.735847946331861</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1586249937053736</v>
+        <v>3.883629243357945</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8043</v>
+        <v>7795</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>718.8097020048684</v>
+        <v>956.226243294316</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>194</v>
+        <v>556</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>58.10481327823487</v>
+        <v>74.67740147161186</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>34.8833398993258</v>
+        <v>20.74456233244841</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.2616443280283657</v>
+        <v>2.722624329431582</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-4.925928791555403</v>
+        <v>15.28850835642637</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6928</v>
+        <v>7402</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>696.1955222267554</v>
+        <v>894</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>54.5</v>
+        <v>115</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>70.54676220279646</v>
+        <v>68.56931796170173</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.20103875082792</v>
+        <v>20.59383443112756</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.219552222675538</v>
+        <v>7.32785698657104</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.7461601312565121</v>
+        <v>2.648868746397813</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8033</v>
+        <v>8040</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>664</v>
+        <v>857.6540513625089</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>169.5</v>
+        <v>112</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>74.86076910770365</v>
+        <v>57.23298053777155</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>16.93536303397059</v>
+        <v>34.20765426112548</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>6.735847946331861</v>
+        <v>0.7718645959272675</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,11 +888,11 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>3.883629243396111</v>
+        <v>0.1586249938198518</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>656.4656684711249</v>
+        <v>846.4656684711249</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>871</v>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>64.09214386836094</v>
+        <v>64.09214388391169</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>32.49938476023846</v>
+        <v>32.49938490566689</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.5342697632805409</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>7.991269302138974</v>
+        <v>7.991269301089602</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6916</v>
+        <v>8046</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>619.3044113938604</v>
+        <v>845.5447837693494</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>20.4</v>
+        <v>1185</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>51.8978335067901</v>
+        <v>71.13006451376665</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>26.75310675714308</v>
+        <v>19.66050020174587</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.1642566690906938</v>
+        <v>0.3368533198374094</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.1670773794318296</v>
+        <v>30.63855684196088</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7402</v>
+        <v>7827</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>619</v>
+        <v>817.952059945118</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>68.56931795637159</v>
+        <v>64.1231149179215</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20.59383442967988</v>
+        <v>21.69806583982458</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7.32785698657104</v>
+        <v>0.4314206803991995</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.648868746245177</v>
+        <v>0.5603778823522845</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6890</v>
+        <v>6901</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>614.0644493532692</v>
+        <v>796.6514518773209</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>197</v>
+        <v>18.8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>41.982061588865</v>
+        <v>70.38449766849574</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>25.95708630260895</v>
+        <v>44.92667152238045</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4401609830275698</v>
+        <v>0.964510538806304</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-7.369100175275722</v>
+        <v>0.235495573367411</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7715</v>
+        <v>8021</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>608.3067127238547</v>
+        <v>775.2939041529685</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>35</v>
+        <v>574</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.72999096209138</v>
+        <v>61.09756603638674</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>43.16093202170421</v>
+        <v>22.27286813466576</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4763893841088874</v>
+        <v>0.3242504193429638</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.4666614006917582</v>
+        <v>-1.835433970750387</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6996</v>
+        <v>7714</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>598.3860541153074</v>
+        <v>757.038882672457</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>195</v>
+        <v>151.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>52.45784005437344</v>
+        <v>69.6481287143209</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.32319496420136</v>
+        <v>24.53527228892217</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.2856909360787437</v>
+        <v>1.46258715948423</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.4820772353442715</v>
+        <v>1.619965339176749</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6901</v>
+        <v>7631</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>596.6514518773209</v>
+        <v>747.2532710930399</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>18.8</v>
+        <v>160</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>70.38449764003492</v>
+        <v>58.35359731461968</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>44.92667144772444</v>
+        <v>17.76800814566355</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.964510538806304</v>
+        <v>3.325327109303982</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.235495573367411</v>
+        <v>4.67823358044492</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7788</v>
+        <v>6962</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>592.3368923302222</v>
+        <v>744.2075989329912</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>257</v>
+        <v>38.65</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.97460856716908</v>
+        <v>54.14097414263345</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>38.12920769204878</v>
+        <v>15.22851767748464</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.034786584855514</v>
+        <v>0.8217087296144302</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-3.298547777032862</v>
+        <v>0.0486700154200118</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6907</v>
+        <v>6957</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>588.5096152023229</v>
+        <v>734.5351297255867</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>146.5</v>
+        <v>190</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>54.48528446883837</v>
+        <v>58.57898621616776</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28.85210466875705</v>
+        <v>22.38698163237824</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.2333486686562007</v>
+        <v>0.3252028367635107</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.3893468994471059</v>
+        <v>-1.026418872460169</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6944</v>
+        <v>6996</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>586.2521395790991</v>
+        <v>733.3860541153074</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>977</v>
+        <v>195</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>51.03285015697903</v>
+        <v>52.45784009151077</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>16.41650040754846</v>
+        <v>22.32319495016065</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.661417224882466</v>
+        <v>0.2856909360787437</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-4.113227946478659</v>
+        <v>-0.4820772353442715</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8032</v>
+        <v>6916</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>584.8961953888262</v>
+        <v>729.3044113938606</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>44.35</v>
+        <v>20.4</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>50.08799056315832</v>
+        <v>51.89783347102766</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>22.30930156538531</v>
+        <v>26.75310678736498</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.3327050238903706</v>
+        <v>0.1642566690906938</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.3919243856720894</v>
+        <v>-0.167077379660782</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6957</v>
+        <v>8043</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>574.5351297255867</v>
+        <v>718.8097020048684</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>58.57898620225884</v>
+        <v>58.10481328228534</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>22.38698168228601</v>
+        <v>34.88333993833336</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.3252028367635107</v>
+        <v>0.2616443280283657</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-1.026418872460169</v>
+        <v>-4.925928791603127</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7714</v>
+        <v>8039</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>557.038882672457</v>
+        <v>696.2217246086969</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>151.5</v>
+        <v>149</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>69.64812864553359</v>
+        <v>54.01714843657268</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>24.53527225835026</v>
+        <v>16.82314286560906</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.46258715948423</v>
+        <v>0.986513386250394</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1.619965339462934</v>
+        <v>-0.281561912091828</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7631</v>
+        <v>7788</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>547.2532710930398</v>
+        <v>652.3368923302222</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>160</v>
+        <v>257</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>58.35359784100392</v>
+        <v>55.97460707342113</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>17.76800826082679</v>
+        <v>38.1292075742975</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>3.325327109303982</v>
+        <v>1.034786584855514</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>4.678233580463997</v>
+        <v>-3.298547747650542</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8039</v>
+        <v>6870</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>541.2217246086969</v>
+        <v>637.8192767800698</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>149</v>
+        <v>263.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>54.01714843254949</v>
+        <v>50.44049431912583</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>16.82314291470187</v>
+        <v>22.06075601221612</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.986513386250394</v>
+        <v>0.2821223781158167</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.2815619121109027</v>
+        <v>-6.934849607748292</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7827</v>
+        <v>7722</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>537.952059945118</v>
+        <v>628.1786623115886</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>173</v>
+        <v>323.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>64.1231149179215</v>
+        <v>54.82739682929252</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>21.69806583982458</v>
+        <v>34.39722736976932</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4314206803991995</v>
+        <v>0.3214481443244145</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.5603778823522845</v>
+        <v>-1.172765641784988</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8046</v>
+        <v>6890</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>530.5444863682509</v>
+        <v>614.0644493532692</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1185</v>
+        <v>197</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>71.13006451051082</v>
+        <v>41.98206167761539</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>19.66050020510794</v>
+        <v>25.95708635871145</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.3368345715753401</v>
+        <v>0.4401609830275698</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>30.63855684218969</v>
+        <v>-7.369100176611298</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6859</v>
+        <v>7715</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>525.4689355499512</v>
+        <v>608.3067127238547</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>47.32108039062452</v>
+        <v>63.72999099368683</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>24.16268026640356</v>
+        <v>43.16093200462348</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4446675768036149</v>
+        <v>0.4763893841088874</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-1.143742224152973</v>
+        <v>0.4666614006726812</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6962</v>
+        <v>7751</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>514.2075989329912</v>
+        <v>602.0865642236801</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>38.65</v>
+        <v>1370</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>54.14097426725304</v>
+        <v>39.62144980323757</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>15.22851753695178</v>
+        <v>13.67852293798259</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8217087296144302</v>
+        <v>0.5030985668905805</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0486700145614432</v>
+        <v>4.764202585186666</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7799</v>
+        <v>6865</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>510.3900052789225</v>
+        <v>597.0111486650378</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>410</v>
+        <v>29.05</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>60.54678110348097</v>
+        <v>53.01353988306634</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>36.39064439333053</v>
+        <v>16.23379742856666</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.597332642500369</v>
+        <v>1.639246129513992</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>5.360643088494102</v>
+        <v>0.7359960801361779</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6870</v>
+        <v>6951</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>497.8192767800697</v>
+        <v>588.5545126814076</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>263.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>50.44049428525177</v>
+        <v>38.85308859836349</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>22.0607559869893</v>
+        <v>27.26489694425931</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.2821223781158167</v>
+        <v>0.5710767979762955</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-6.934849607652847</v>
+        <v>-0.3122373008243784</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7751</v>
+        <v>6907</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>492.0865642236801</v>
+        <v>588.5096152023229</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1370</v>
+        <v>146.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>39.62144980120328</v>
+        <v>54.48528446883837</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>13.67852293794657</v>
+        <v>28.85210466875705</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5030985668905805</v>
+        <v>0.2333486686562007</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>4.764202585759051</v>
+        <v>-0.3893468994471059</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7722</v>
+        <v>6944</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>458.1786623115887</v>
+        <v>586.2521395790991</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>323.5</v>
+        <v>977</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>54.8273968217304</v>
+        <v>51.0328501683589</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>34.39722739884536</v>
+        <v>16.41650043299081</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3214481443244145</v>
+        <v>0.661417224882466</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-1.172765642357456</v>
+        <v>-4.113227947718798</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6894</v>
+        <v>8032</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>445.6279758757601</v>
+        <v>584.8961953888262</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>363.5</v>
+        <v>44.35</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>49.66565379615131</v>
+        <v>50.08799067887507</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>21.8527167452555</v>
+        <v>22.3093015518836</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.284862212498241</v>
+        <v>0.3327050238903706</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-1.476668793910758</v>
+        <v>-0.3919243858819617</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6877</v>
+        <v>6967</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>439.5151636836093</v>
+        <v>580.7954429093559</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>122</v>
+        <v>72.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>36.96802207821641</v>
+        <v>54.02133433994256</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>19.51350633058205</v>
+        <v>9.635088466003671</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.598440263354916</v>
+        <v>0.2814459072922928</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.8507983552792631</v>
+        <v>0.2199341380697881</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7749</v>
+        <v>6903</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>439.3338133030598</v>
+        <v>569.1216110417016</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>423</v>
+        <v>388</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>36.00817939585208</v>
+        <v>49.9347829817694</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20.12683093430202</v>
+        <v>11.09008186896041</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4024324964827885</v>
+        <v>1.194937185561272</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-9.334748041552515</v>
+        <v>-0.8943692512850032</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7768</v>
+        <v>6906</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>436.6194492660444</v>
+        <v>553.8989618314586</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>342.5</v>
+        <v>88.8</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>37.64599249330485</v>
+        <v>49.47087577906526</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>21.84687525860289</v>
+        <v>21.54476761007268</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.311142902182893</v>
+        <v>0.3364496408887801</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-4.392750192325773</v>
+        <v>-1.400809879538745</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6902</v>
+        <v>6859</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>424.5174484933663</v>
+        <v>525.4689355499512</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>128.5</v>
+        <v>125</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>47.55624430421484</v>
+        <v>47.32108033796165</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23.37951028031054</v>
+        <v>24.16268026842845</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.2181804405904646</v>
+        <v>0.4446675768036149</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.989170639425948</v>
+        <v>-1.143742223389792</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7822</v>
+        <v>6862</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>421.7854017352822</v>
+        <v>524.148800128641</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1080</v>
+        <v>201.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45.28477489878881</v>
+        <v>52.09537547951668</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>18.28041071547305</v>
+        <v>21.37326946055751</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4202325943594956</v>
+        <v>0.4026224750738044</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>5.299805213739532</v>
+        <v>-1.980435606982614</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6906</v>
+        <v>7744</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>413.8989618314585</v>
+        <v>514.0163110021093</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>88.8</v>
+        <v>453</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>49.47087577906526</v>
+        <v>41.6911356252259</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>21.54476708162356</v>
+        <v>14.30627357168061</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3364496408887801</v>
+        <v>0.2602892776008897</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-1.400809879538745</v>
+        <v>-2.48408424585814</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6862</v>
+        <v>7799</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>409.1488001286411</v>
+        <v>510.3900052789226</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>201.5</v>
+        <v>410</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>52.09537550235104</v>
+        <v>60.54678117344967</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.37326958987702</v>
+        <v>36.39064440094266</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4026224750738044</v>
+        <v>1.597332642500369</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-1.980435608699772</v>
+        <v>5.360643087158577</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6903</v>
+        <v>7747</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>409.1216110417016</v>
+        <v>491.8441531696446</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>388</v>
+        <v>129</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>49.93478296284364</v>
+        <v>52.71755002850767</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>11.09008185874874</v>
+        <v>4.876190569535154</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.194937185561272</v>
+        <v>0.3717165382917541</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.8943692513803638</v>
+        <v>-0.2253133655463735</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6861</v>
+        <v>7760</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>409.1081647541209</v>
+        <v>481.2070146388879</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>333</v>
+        <v>33</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>47.12314399196535</v>
+        <v>50.6859020976174</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.52770474284613</v>
+        <v>39.03798042616654</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4482348931151581</v>
+        <v>0.5812095392592368</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-3.498409509671066</v>
+        <v>0.1760133753377231</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6919</v>
+        <v>7556</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>406.8839470563673</v>
+        <v>474.996979373137</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>99.8</v>
+        <v>280</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.51770696547804</v>
+        <v>52.13157780929895</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.5419235349903</v>
+        <v>11.26549764497539</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3072040493886019</v>
+        <v>0.3091051685142151</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2343758248892888</v>
+        <v>-0.8219674371384391</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>7744</v>
+        <v>7803</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>399.0163110021093</v>
+        <v>472.4007425855717</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>453</v>
+        <v>23.75</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>41.6911356252259</v>
+        <v>49.92499462395326</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>14.30627356922393</v>
+        <v>19.49422682551932</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.2602892776008897</v>
+        <v>1.118193644888006</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-2.484084245762741</v>
+        <v>0.3054551174564854</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7805</v>
+        <v>7703</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>398.3262252146002</v>
+        <v>468.8897021915016</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>661</v>
+        <v>200.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>35.59370908321112</v>
+        <v>45.85964765105867</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>27.91786330525746</v>
+        <v>11.23458745490562</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4652894748487213</v>
+        <v>0.6512764740717124</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-6.257031714472877</v>
+        <v>0.07840986326621641</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6865</v>
+        <v>7721</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>397.0111486650377</v>
+        <v>467.8977311689316</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>29.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>53.01353976314679</v>
+        <v>44.50363699180727</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>16.2337975331178</v>
+        <v>12.6841007365969</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.639246129513992</v>
+        <v>0.3027204723243599</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.7359960808993588</v>
+        <v>-0.9274233176189344</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6969</v>
+        <v>6863</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>391.2938592899568</v>
+        <v>457.4001494568728</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>23.75</v>
+        <v>91.8</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>12.67205571538094</v>
+        <v>35.54538945224306</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>29.68126793159643</v>
+        <v>25.047277252401</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.233189204291842</v>
+        <v>0.7887554689917095</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.2403344631274582</v>
+        <v>-0.6461980344930112</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7750</v>
+        <v>6894</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>380.5478923349908</v>
+        <v>445.6279758757601</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2010</v>
+        <v>363.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>40.37435191420445</v>
+        <v>49.66565381380841</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>20.36960341235994</v>
+        <v>21.8527167452555</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4386361310850526</v>
+        <v>0.284862212498241</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-24.24460775510047</v>
+        <v>-1.476668793910758</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7711</v>
+        <v>7738</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>376.6442015483646</v>
+        <v>443.8895671769641</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>320.5</v>
+        <v>167</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>35.74536815082807</v>
+        <v>42.69868740222462</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>19.20675750878524</v>
+        <v>21.95885460869913</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3586579122643655</v>
+        <v>0.3071024364297218</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-5.055956953187604</v>
+        <v>-0.150351508282879</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7769</v>
+        <v>7822</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>368.4621257964762</v>
+        <v>441.7854017352822</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>6470</v>
+        <v>1080</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>42.18006364652416</v>
+        <v>45.28477491594574</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>18.09312199396032</v>
+        <v>18.28041092242549</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.8948823950109519</v>
+        <v>0.4202325943594956</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-136.2153930562167</v>
+        <v>5.299805210877686</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8044</v>
+        <v>6877</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>364.1981958630522</v>
+        <v>439.5151636836093</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>28.2</v>
+        <v>122</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>46.8452943323652</v>
+        <v>36.96802214746635</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.70926278149343</v>
+        <v>19.51350663150181</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4094565154980853</v>
+        <v>1.598440263354916</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.3936074945702841</v>
+        <v>-0.8507983563286086</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6951</v>
+        <v>7749</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>363.5545126814076</v>
+        <v>439.3338133030598</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>423</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>38.85308857949719</v>
+        <v>36.00817939585208</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>27.264896842872</v>
+        <v>20.12683093430202</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5710767979762955</v>
+        <v>0.4024324964827885</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.3122373008434648</v>
+        <v>-9.334748041552515</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7820</v>
+        <v>6971</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>360.0913312114853</v>
+        <v>438.5088419589216</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>111.5</v>
+        <v>27.95</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>31.37874575458784</v>
+        <v>54.58511213678419</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>28.23935615481996</v>
+        <v>22.08669265469977</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5606018556716496</v>
+        <v>0.2470418952761724</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.5057145261514506</v>
+        <v>0.1414409536593686</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7556</v>
+        <v>7768</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>359.996979373137</v>
+        <v>436.6194492660444</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>280</v>
+        <v>342.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.13157776418466</v>
+        <v>37.64599249945026</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>11.26549761725188</v>
+        <v>21.84687542272923</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3091051685142151</v>
+        <v>0.311142902182893</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.8219674372338601</v>
+        <v>-4.392750192611949</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6955</v>
+        <v>6952</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>358.2301418737239</v>
+        <v>432.4367811673205</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>121.5</v>
+        <v>35.9</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.3124823265112</v>
+        <v>43.39284295350031</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>10.98613245855194</v>
+        <v>21.17545801079364</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>3.83972955194551</v>
+        <v>0.3580725476260034</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-5.856266202148263</v>
+        <v>0.0482930529479231</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7703</v>
+        <v>7823</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>353.8897021915016</v>
+        <v>429.1625668013757</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>200.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45.85964762487184</v>
+        <v>25.72673564140352</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>11.2345874847799</v>
+        <v>32.90391507831423</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6512764740717124</v>
+        <v>0.1861328270816224</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.07840986345702421</v>
+        <v>-0.5724251874056256</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7721</v>
+        <v>6910</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>352.8977311689316</v>
+        <v>428.2160713099379</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>27.35</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>44.50363703325614</v>
+        <v>40.10197800347619</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12.68410074384802</v>
+        <v>15.21052365354505</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3027204723243599</v>
+        <v>0.4934379718272469</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.9274233178860511</v>
+        <v>-0.1202474275506963</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7792</v>
+        <v>6902</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>351.9469985317348</v>
+        <v>424.5174484933663</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>258.5</v>
+        <v>128.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>42.7909429202012</v>
+        <v>47.5562443482663</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.32019996955977</v>
+        <v>23.37951033193257</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3216644059004642</v>
+        <v>0.2181804405904646</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.6893105960529411</v>
+        <v>-1.989170639578585</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7747</v>
+        <v>8044</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>351.8441531696446</v>
+        <v>424.1981958630522</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>129</v>
+        <v>28.2</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.71755004218008</v>
+        <v>46.84529435887914</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>4.876190558757505</v>
+        <v>19.7092627286807</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3717165382917541</v>
+        <v>0.4094565154980853</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.2253133657371782</v>
+        <v>-0.3936074947229194</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7704</v>
+        <v>7705</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>347.8238252198855</v>
+        <v>416.7448133005087</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>62.4</v>
+        <v>31.7</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.58327708918801</v>
+        <v>49.51601272710735</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>12.21497662586652</v>
+        <v>18.16287970871124</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.313924734033579</v>
+        <v>0.7107050687065998</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.2684327210019005</v>
+        <v>0.0523655206823086</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6983</v>
+        <v>6873</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>347.2719102000331</v>
+        <v>415.0010977368373</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>354.5</v>
+        <v>82.3</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45.12015243269564</v>
+        <v>46.10497754822541</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>10.93016832846117</v>
+        <v>12.40840714455878</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.1777949852946027</v>
+        <v>0.3103933850732653</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>2.106468428683289</v>
+        <v>0.1097654792849072</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7760</v>
+        <v>7810</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>341.2070146388879</v>
+        <v>414.2024093990029</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>33</v>
+        <v>207.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.68590191293826</v>
+        <v>46.58760557382548</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>39.03798043264389</v>
+        <v>14.1817108457231</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5812095392592368</v>
+        <v>1.067400480276474</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1760133755380606</v>
+        <v>-0.0316125540057719</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7734</v>
+        <v>6924</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>340.1653182046583</v>
+        <v>412.3324266117995</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>3035</v>
+        <v>120.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>44.94678204162159</v>
+        <v>43.010530157937</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.48857828777618</v>
+        <v>22.63266242195347</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.2191611874590434</v>
+        <v>0.5374753451676528</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-27.75924603837629</v>
+        <v>-1.733843431104763</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6967</v>
+        <v>6969</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>330.7954429093558</v>
+        <v>411.2938592899567</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>72.7</v>
+        <v>23.75</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>54.02133428225694</v>
+        <v>12.67205569777866</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>9.635088470916802</v>
+        <v>29.68126793489439</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2814459072922928</v>
+        <v>2.233189204291842</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.2199341382701088</v>
+        <v>-0.2403344631179177</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7738</v>
+        <v>7818</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>328.8895671769641</v>
+        <v>409.6449226361562</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>167</v>
+        <v>63.3</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>42.69868726319091</v>
+        <v>34.0593336278092</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21.95885465679848</v>
+        <v>46.66930635780065</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3071024364297218</v>
+        <v>0.5795783311297882</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.150351508282879</v>
+        <v>1.404950900267028</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7753</v>
+        <v>6861</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>328.2647973442806</v>
+        <v>409.1081647541209</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>42.35</v>
+        <v>333</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>48.78850265281147</v>
+        <v>47.12314399518678</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.31833738943079</v>
+        <v>20.52770470387664</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.2842845029449076</v>
+        <v>0.4482348931151581</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0014758912205505</v>
+        <v>-3.498409509537491</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6971</v>
+        <v>6919</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>323.5088419589216</v>
+        <v>406.8839470563673</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>27.95</v>
+        <v>99.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>54.58511186335282</v>
+        <v>49.5177069451022</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.08669261182532</v>
+        <v>16.54192347109124</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.2470418952761724</v>
+        <v>0.3072040493886019</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.1414409537452246</v>
+        <v>0.2343758257303138</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6863</v>
+        <v>8047</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>322.4001494568728</v>
+        <v>404.8102512410449</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>91.8</v>
+        <v>48.9</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>35.5453892311466</v>
+        <v>50.19900384583487</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>25.04727724037915</v>
+        <v>6.285875146498471</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7887554689917095</v>
+        <v>0.0309263420311105</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.6461980337298399</v>
+        <v>-0.0976441855057868</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8038</v>
+        <v>6914</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>313.9487889225067</v>
+        <v>402.4331150997845</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>39.35</v>
+        <v>143</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>42.55133031377245</v>
+        <v>51.42945314879667</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>7.264826922541632</v>
+        <v>10.70796677503756</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4245589270568923</v>
+        <v>0.4018960557929242</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.160256652550924</v>
+        <v>0.2560329280700072</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6910</v>
+        <v>7805</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>313.2160713099379</v>
+        <v>398.3262252146002</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>27.35</v>
+        <v>661</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>40.10197819581784</v>
+        <v>35.5937091314714</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.2105235983203</v>
+        <v>27.91786328681689</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4934379718272469</v>
+        <v>0.4652894748487213</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1202474277414895</v>
+        <v>-6.257031715236092</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7786</v>
+        <v>6953</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>302.4676197749629</v>
+        <v>393.3625957932496</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>123</v>
+        <v>232</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.06009065365703</v>
+        <v>46.61419269754076</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.00746325348463</v>
+        <v>18.19937561699173</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.597555644461508</v>
+        <v>0.3190926716166685</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0361969500637151</v>
+        <v>0.3670164392620325</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7823</v>
+        <v>6918</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>294.1625668013757</v>
+        <v>390.7996929173095</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>25.72673564140352</v>
+        <v>41.3883116001692</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>32.90391507831423</v>
+        <v>6.820710264901946</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.1861328270816224</v>
+        <v>5.139866255255106</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.5724251874056256</v>
+        <v>-0.0611448302168802</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6952</v>
+        <v>7750</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>292.4367811673204</v>
+        <v>380.6087360500337</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>35.9</v>
+        <v>2010</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>43.39284287036126</v>
+        <v>40.37435191858221</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21.17545800981852</v>
+        <v>20.36960341247821</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.3580725476260034</v>
+        <v>0.4457565601843611</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0482930528525198</v>
+        <v>-24.24460775490951</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>7717</v>
+        <v>7780</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>291.0547692689225</v>
+        <v>380.1352115401919</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>440</v>
+        <v>18.15</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>28.88202421513805</v>
+        <v>44.61780323061188</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.17447673322776</v>
+        <v>16.16281874413008</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4969775320470404</v>
+        <v>0.5421631954688998</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-11.07849408071436</v>
+        <v>-0.0263231480438767</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6914</v>
+        <v>7711</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>287.4331150997845</v>
+        <v>376.6442015483646</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>143</v>
+        <v>320.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.42945305389114</v>
+        <v>35.74536819144458</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>10.70796682547939</v>
+        <v>19.20675759903547</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4018960557929242</v>
+        <v>0.3586579122643655</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.2560329280700072</v>
+        <v>-5.055956954046163</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6887</v>
+        <v>6994</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>281.990049839329</v>
+        <v>372.209370154871</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>35.7</v>
+        <v>48.15</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.98618364092603</v>
+        <v>30.28043496118272</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>6.738066361515385</v>
+        <v>25.20993241047788</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.1372415858926076</v>
+        <v>1.342658251294513</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.2099528232095364</v>
+        <v>-0.7661764069105459</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7705</v>
+        <v>7730</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>281.7448133005087</v>
+        <v>370.2312739988877</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>31.7</v>
+        <v>188</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.51601285819801</v>
+        <v>52.20180658587868</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>18.16287971847936</v>
+        <v>12.2844566652381</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7107050687065998</v>
+        <v>0.3389297034528121</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0523655206250662</v>
+        <v>-0.0603263905161384</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6953</v>
+        <v>7769</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>278.3625957932496</v>
+        <v>368.6052276905352</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>232</v>
+        <v>6470</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>46.61419267703309</v>
+        <v>42.18006365093281</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.19937543601439</v>
+        <v>18.09312198596947</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3190926716166685</v>
+        <v>0.9074662272243424</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.3670164386896735</v>
+        <v>-136.2153930579338</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7818</v>
+        <v>7839</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>274.6449226361562</v>
+        <v>366.0823166108789</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>63.3</v>
+        <v>45.25</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>34.0593336117479</v>
+        <v>44.26957302767716</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>46.66930635703039</v>
+        <v>8.770019276055145</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5795783311297882</v>
+        <v>0.3016592957889855</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>1.404950900648631</v>
+        <v>-0.8819497961208134</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6922</v>
+        <v>7717</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>274.3423375468745</v>
+        <v>366.0547692689225</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>174</v>
+        <v>440</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>42.63299187409242</v>
+        <v>28.88202421513805</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.80382975163102</v>
+        <v>19.17447673322776</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3367398021126176</v>
+        <v>0.4969775320470404</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-2.429147760345461</v>
+        <v>-11.07849408071436</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7810</v>
+        <v>6937</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>274.2024093990029</v>
+        <v>364.5560718712994</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>207.5</v>
+        <v>268</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>46.58760556673472</v>
+        <v>44.49223242363357</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.18171078894644</v>
+        <v>13.76545558837595</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.067400480276474</v>
+        <v>0.5219700910683422</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0316125538912572</v>
+        <v>-1.204524711505382</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6924</v>
+        <v>6855</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>272.3324266117995</v>
+        <v>364.3691424771512</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>120.5</v>
+        <v>122</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>43.01053070468689</v>
+        <v>52.23942502305134</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>22.63266240685774</v>
+        <v>12.74829316970637</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5374753451676528</v>
+        <v>0.5598112289494873</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-1.733843430952131</v>
+        <v>0.5462608288541357</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6909</v>
+        <v>7820</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>271.1068143462281</v>
+        <v>360.0913312114853</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>55.1</v>
+        <v>111.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>54.73100854788866</v>
+        <v>31.37874571621164</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>18.31905483555268</v>
+        <v>28.23935620855181</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5424119135112264</v>
+        <v>0.5606018556716496</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.9679770951243714</v>
+        <v>0.5057145263231657</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8034</v>
+        <v>6955</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>267.4130753776759</v>
+        <v>358.2301418737239</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>21.8</v>
+        <v>121.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>29.4657242918579</v>
+        <v>49.31248296950741</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.04274523161229</v>
+        <v>10.98613351153088</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.2753713641644597</v>
+        <v>3.83972955194551</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.1557701120516018</v>
+        <v>-5.85626622981345</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8047</v>
+        <v>6936</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>264.8102512410449</v>
+        <v>353.6698837136498</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>48.9</v>
+        <v>32.75</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>50.19900384734266</v>
+        <v>42.8972626693518</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>6.285875217704315</v>
+        <v>12.23566896805514</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.0309263420311105</v>
+        <v>0.6312740900567799</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.09764418551532519</v>
+        <v>-0.07176121565672</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7842</v>
+        <v>7792</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>264.5865524056053</v>
+        <v>351.9469985317348</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>96.8</v>
+        <v>258.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>33.23845692990767</v>
+        <v>42.79094299052365</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>25.40039308829948</v>
+        <v>18.32019996955977</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4974407717239221</v>
+        <v>0.3216644059004642</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.5037656526397072</v>
+        <v>0.6893105960529411</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6994</v>
+        <v>7704</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>262.543790353479</v>
+        <v>347.8238252198855</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>48.15</v>
+        <v>62.4</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>30.28043485142824</v>
+        <v>52.58327713724244</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>25.20993241001593</v>
+        <v>12.21497659370298</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.322667646347046</v>
+        <v>0.313924734033579</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.7661764063381624</v>
+        <v>0.2684327209828204</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6965</v>
+        <v>6983</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>260.3567403047742</v>
+        <v>347.2719102000331</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>76.5</v>
+        <v>354.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>36.09648606330591</v>
+        <v>45.12015332855204</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>23.69528608249826</v>
+        <v>10.93016910338247</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3912929282317144</v>
+        <v>0.1777949852946027</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.3465601531799299</v>
+        <v>2.106468408077484</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6958</v>
+        <v>7772</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>259.3548575801759</v>
+        <v>343.5608416827102</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>16.6</v>
+        <v>130</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>42.19661551783107</v>
+        <v>38.84913729538695</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16.04756774725309</v>
+        <v>9.21110398551242</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.0813585043524692</v>
+        <v>0.2070127715543332</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0308780983283198</v>
+        <v>-1.040108290092131</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7732</v>
+        <v>7734</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>256.9786545051209</v>
+        <v>340.1653182046583</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0</v>
+        <v>3035</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>38.47046221102853</v>
+        <v>44.94678205485499</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.14440320231437</v>
+        <v>18.48857825305045</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.000498487919976</v>
+        <v>0.2191611874590434</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-1.909190573345103</v>
+        <v>-27.75924603742222</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6873</v>
+        <v>7753</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>255.0010977368375</v>
+        <v>328.2647973442806</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>82.3</v>
+        <v>42.35</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.10497742377518</v>
+        <v>48.78850263968216</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12.40840698410701</v>
+        <v>20.31833738509709</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3103933850732653</v>
+        <v>0.2842845029449076</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1097654790941189</v>
+        <v>0.0014758912205505</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6937</v>
+        <v>7770</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>254.5560718712995</v>
+        <v>325.5165101771333</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>268</v>
+        <v>42.35</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>44.49223239366843</v>
+        <v>48.26337456773933</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.76545555414205</v>
+        <v>5.896099312410081</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5219700910683422</v>
+        <v>0.9123708989763114</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-1.204524711314573</v>
+        <v>0.0398763217564841</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7821</v>
+        <v>6931</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>239.3430819856596</v>
+        <v>314.2480650689185</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>41.9</v>
+        <v>39.8</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>35.97324459496745</v>
+        <v>35.71011030802875</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>21.65122859187897</v>
+        <v>17.02583154378264</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3977942079191258</v>
+        <v>0.5598069132838255</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1127042803574116</v>
+        <v>0.0935667641382698</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6997</v>
+        <v>8038</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>237.7464765530874</v>
+        <v>313.9487889225069</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>73</v>
+        <v>39.35</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>51.16055690725027</v>
+        <v>42.55133028446557</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>7.473096480310628</v>
+        <v>7.264826932805615</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.8026709219638404</v>
+        <v>0.4245589270568923</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.3618779238929861</v>
+        <v>-0.1602566525604637</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7772</v>
+        <v>7786</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>233.5608416827102</v>
+        <v>302.467619774963</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>38.84913729538695</v>
+        <v>46.06009057867758</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>9.21110398551242</v>
+        <v>18.00746330886058</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.2070127715543332</v>
+        <v>0.597555644461508</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-1.040108290092131</v>
+        <v>-0.0361969494913284</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>7765</v>
+        <v>6899</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>233.4157598077684</v>
+        <v>295.6172847372845</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>221.5</v>
+        <v>57.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>35.22952160358446</v>
+        <v>40.06261625232517</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>26.45049292325333</v>
+        <v>17.4975449937353</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8558703132727904</v>
+        <v>0.2342034481963964</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-3.278364516721707</v>
+        <v>-0.6935887619642126</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7728</v>
+        <v>7842</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>227.1904385277977</v>
+        <v>284.5865524056053</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>666</v>
+        <v>96.8</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>40.37722190346647</v>
+        <v>33.23845692990767</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>10.66895980520141</v>
+        <v>25.40039308829948</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6064663298422436</v>
+        <v>0.4974407717239221</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-5.808077885923259</v>
+        <v>0.5037656526397072</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7547</v>
+        <v>6908</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>225.3300287746144</v>
+        <v>283.8211321712907</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>56.9</v>
+        <v>37.4</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>37.98688808417726</v>
+        <v>37.97815557118352</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>16.06027772114437</v>
+        <v>11.08596100113687</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5697817065511513</v>
+        <v>0.183094293561184</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0665041675929685</v>
+        <v>-0.1164452143481399</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6988</v>
+        <v>6887</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>222.3596659708342</v>
+        <v>281.990049839329</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>13.45</v>
+        <v>35.7</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>31.77528401662178</v>
+        <v>50.98618367014749</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>14.49185235551691</v>
+        <v>6.73806637566415</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4871926039034384</v>
+        <v>0.1372415858926076</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0598059680021165</v>
+        <v>0.2099528230950583</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6933</v>
+        <v>6958</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>221.1243336001698</v>
+        <v>279.3548575801759</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>142</v>
+        <v>16.6</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>38.41152394485163</v>
+        <v>42.19661551783107</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>22.31208464487138</v>
+        <v>16.04756776382584</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.26662158371498</v>
+        <v>0.0813585043524692</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-1.636528382239998</v>
+        <v>-0.0308780983283198</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6936</v>
+        <v>6922</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>213.6698837136498</v>
+        <v>274.3423375468745</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>32.75</v>
+        <v>174</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.89726187590944</v>
+        <v>42.63299203063008</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>12.23566894160978</v>
+        <v>16.80382975879873</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6312740900567799</v>
+        <v>0.3367398021126176</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0717612156948797</v>
+        <v>-2.429147760917852</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7770</v>
+        <v>6909</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>210.5165101771333</v>
+        <v>271.1068143462281</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>42.35</v>
+        <v>55.1</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>48.26337450162968</v>
+        <v>54.73100854511234</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>5.896099310617754</v>
+        <v>18.31905486311753</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.9123708989763114</v>
+        <v>0.5424119135112264</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0398763220808328</v>
+        <v>0.9679770949717288</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8045</v>
+        <v>8034</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>209.5513165664763</v>
+        <v>267.4130753776756</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>58.9</v>
+        <v>21.8</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>36.8180029484483</v>
+        <v>29.46572431490124</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>12.66443527946266</v>
+        <v>22.0427452376278</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.2861266867478583</v>
+        <v>0.2753713641644597</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.06667892280378</v>
+        <v>-0.1557701120420647</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6925</v>
+        <v>6965</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>207.5735338062453</v>
+        <v>260.3567403047742</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>59.5</v>
+        <v>76.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>41.41243279070683</v>
+        <v>36.09648603200348</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15.46296797564221</v>
+        <v>23.69528636659953</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.07991961978632391</v>
+        <v>0.3912929282317144</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.8463638029238528</v>
+        <v>-0.3465601526075531</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6913</v>
+        <v>7821</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>199.9676202275448</v>
+        <v>259.3430819856596</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>119.5</v>
+        <v>41.9</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>39.58122265934312</v>
+        <v>35.97324472085458</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>16.78090512344701</v>
+        <v>21.65122859619873</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.500602844827658</v>
+        <v>0.3977942079191258</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.968785792041272</v>
+        <v>-0.1127042805386644</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6869</v>
+        <v>7732</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>199.9595639125695</v>
+        <v>256.978654505121</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>72.5</v>
+        <v>0</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>35.89124554791861</v>
+        <v>38.47046221359201</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>22.94960501236323</v>
+        <v>15.14440313679719</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4294814046709557</v>
+        <v>0.000498487919976</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.623298273208607</v>
+        <v>-1.90919057345958</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6934</v>
+        <v>6933</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>194.5344713212063</v>
+        <v>241.1243336001698</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>33.57714207918626</v>
+        <v>38.41152401125356</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>22.78108531672159</v>
+        <v>22.31208465635339</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.8002679854127528</v>
+        <v>0.26662158371498</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0919334792156614</v>
+        <v>-1.636528382335385</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6092,21 +6092,21 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6855</v>
+        <v>6997</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>194.3691424771513</v>
+        <v>237.7464765530874</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>52.23942502305134</v>
+        <v>51.1605562440712</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.74829313487235</v>
+        <v>7.47309614223559</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5598112289494873</v>
+        <v>0.8026709219638404</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.5462608288541357</v>
+        <v>0.3618779439263909</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7803</v>
+        <v>7765</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>192.4007425855717</v>
+        <v>233.4157598077684</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>23.75</v>
+        <v>221.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>49.92499471909053</v>
+        <v>35.22952163420717</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>19.49422681528483</v>
+        <v>26.4504929146844</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.118193644888006</v>
+        <v>0.8558703132727904</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.305455117475566</v>
+        <v>-3.278364516721707</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6918</v>
+        <v>6925</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>187.8529534837438</v>
+        <v>227.5735338062453</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>72.3</v>
+        <v>59.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>41.38831162044566</v>
+        <v>41.41243281755204</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>6.820710216024727</v>
+        <v>15.46296796562921</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.9425649574519344</v>
+        <v>0.07991961978632391</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.061144829644497</v>
+        <v>-0.846363803267282</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6899</v>
+        <v>7728</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>185.6172847372845</v>
+        <v>227.1904385277977</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>57.5</v>
+        <v>666</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>40.06261622167133</v>
+        <v>40.37722192554613</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.49754495256337</v>
+        <v>10.66895987276291</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.2342034481963964</v>
+        <v>0.6064663298422436</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.6935887617734158</v>
+        <v>-5.808077887449612</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7740</v>
+        <v>7547</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>185.4468506478645</v>
+        <v>225.3300287746144</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>151.5</v>
+        <v>56.9</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.05106353699558</v>
+        <v>37.98688808417726</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.36847381246887</v>
+        <v>16.06027776794566</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5978832690290758</v>
+        <v>0.5697817065511513</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-1.521254827737332</v>
+        <v>0.0665041675929685</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6854</v>
+        <v>6988</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>181.1500273049598</v>
+        <v>222.3596659708342</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>124</v>
+        <v>13.45</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>36.69439306262073</v>
+        <v>31.77527675239521</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.76601776100621</v>
+        <v>14.49185121896711</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.732794616262882</v>
+        <v>0.4871926039034384</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.296108737668983</v>
+        <v>-0.0598059643007044</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6931</v>
+        <v>8045</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>179.2480650689185</v>
+        <v>209.5513165664763</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>39.8</v>
+        <v>58.9</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>35.71011036391572</v>
+        <v>36.81800304397508</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.02583150269241</v>
+        <v>12.66443524726284</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5598069132838255</v>
+        <v>0.2861266867478583</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0935667640237951</v>
+        <v>-0.0666789229182613</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6895</v>
+        <v>8011</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>176.0899212542587</v>
+        <v>207.9988223121258</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>146</v>
+        <v>17.7</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>39.5843664822227</v>
+        <v>44.87734788543212</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>17.38940325553931</v>
+        <v>17.31498277476537</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.005586308064039</v>
+        <v>1.009935348749123</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-1.851190113631076</v>
+        <v>-0.0553029256096879</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>7839</v>
+        <v>7740</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>176.0823166108788</v>
+        <v>205.4468506478645</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>45.25</v>
+        <v>151.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.26957302767716</v>
+        <v>41.05106358338048</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8.770019276055145</v>
+        <v>17.36847379199387</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.3016592957889855</v>
+        <v>0.5978832690290758</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.8819497961208134</v>
+        <v>-1.521254828023518</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6908</v>
+        <v>6913</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>173.8211321712907</v>
+        <v>199.9676202275448</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>37.4</v>
+        <v>119.5</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>37.97815557911517</v>
+        <v>39.58122291093808</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>11.08596093793338</v>
+        <v>16.78090517489365</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.183094293561184</v>
+        <v>0.500602844827658</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.1164452143481399</v>
+        <v>-0.9687857924228468</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7736</v>
+        <v>6869</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>165.7050162190411</v>
+        <v>199.9595639125684</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>70.8</v>
+        <v>72.5</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>40.26291294426612</v>
+        <v>35.89124581272385</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>13.97508765304437</v>
+        <v>22.94960496656421</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.6796934473397426</v>
+        <v>0.4294814046709557</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0499279048660236</v>
+        <v>-0.6232982750211473</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6923</v>
+        <v>6934</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>162.2085742327962</v>
+        <v>194.5344713212063</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>74.2</v>
+        <v>65</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>37.60978140771616</v>
+        <v>33.57714360268015</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>14.00308280431949</v>
+        <v>22.78108528767524</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.3630947452009537</v>
+        <v>0.8002679854127528</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.4081223387406083</v>
+        <v>-0.091933490625176</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7780</v>
+        <v>6885</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>155.1352115401918</v>
+        <v>190.7422954711773</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>18.15</v>
+        <v>21.35</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>44.61780294636997</v>
+        <v>41.65011702998852</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>16.16281877828002</v>
+        <v>17.04279878849849</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5421631954688998</v>
+        <v>0.4875401139857598</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0263231474383444</v>
+        <v>-0.228955517803918</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6921</v>
+        <v>6854</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>138.3202614109276</v>
+        <v>181.1500273049598</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>68.5</v>
+        <v>124</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>37.00953884682142</v>
+        <v>36.6943931583653</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>19.59704935602863</v>
+        <v>19.76601771029725</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5285749877349969</v>
+        <v>0.732794616262882</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.2017187529938628</v>
+        <v>-0.2961087386229843</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>7730</v>
+        <v>6895</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>120.2312739988877</v>
+        <v>176.0899212542584</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>52.2018065823551</v>
+        <v>39.5843665267236</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>12.28445662102877</v>
+        <v>17.38940322059512</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.3389297034528121</v>
+        <v>1.005586308064039</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0603263907641462</v>
+        <v>-1.8511901135357</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>8011</v>
+        <v>7791</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>67.99882231212581</v>
+        <v>166.0818288470099</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>17.7</v>
+        <v>61.9</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>44.87734785123306</v>
+        <v>39.41700465523046</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>17.314982807604</v>
+        <v>17.54981815640386</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.009935348749123</v>
+        <v>0.2087090133755731</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0553029256001506</v>
+        <v>-0.1475838052539234</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6885</v>
+        <v>7736</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>55.74229547117754</v>
+        <v>165.7050162190411</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>21.35</v>
+        <v>70.8</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>41.65011695239141</v>
+        <v>40.2629131928766</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17.04279858595271</v>
+        <v>13.97508766000986</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.4875401139857598</v>
+        <v>0.6796934473397426</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.2289555176417455</v>
+        <v>-0.0499279051522261</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7791</v>
+        <v>6923</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>51.08182884701002</v>
+        <v>162.2085742327963</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>61.9</v>
+        <v>74.2</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>39.41700483146788</v>
+        <v>37.6097814369287</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.54981797432722</v>
+        <v>14.0030828194566</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.2087090133755731</v>
+        <v>0.3630947452009537</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,11 +7036,64 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.1475838055401201</v>
+        <v>-0.4081223385688912</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>6921</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>嘉雨思-創</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>138.3202614109276</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>37.00953884682142</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>19.59704935602863</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.5285749877349969</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>0.2017187529938628</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
